--- a/backend-print/App_Data/b-templates/equipment_master_detail.xlsx
+++ b/backend-print/App_Data/b-templates/equipment_master_detail.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\app_data\b-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kotem\OneDrive\Documents\cs-work\GemboxPrintApi\backend-print\App_Data\b-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA408A3-E3E6-414F-B7E8-8C12EAB3D8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7791A5F3-442E-4617-9F25-70B2665A3417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3621150-4E95-40DC-AB77-EDF48FFCF4AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet2!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>機器名</t>
     <rPh sb="0" eb="2">
@@ -171,10 +173,6 @@
   </si>
   <si>
     <t>{{equipment_code}}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>a</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -358,7 +356,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -371,60 +369,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -441,6 +409,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE738C4F-52F5-4653-BCD1-C5F716DA4766}">
-  <dimension ref="A2:L46"/>
+  <dimension ref="B2:K19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:11" ht="33" x14ac:dyDescent="0.4">
@@ -787,236 +782,236 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="21"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="24"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="27"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="15"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="17"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="15"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="17"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="15"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="17"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="8"/>
+      <c r="D11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="15"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="17"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="8"/>
+      <c r="D13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="15"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="17"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="15"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B17" s="14" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="14" t="s">
+      <c r="C17" s="8"/>
+      <c r="D17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B18" s="9"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -1028,111 +1023,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="23" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="D11:K12"/>
-    <mergeCell ref="D13:K14"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="D3:K4"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D15:K16"/>
+  <mergeCells count="17">
     <mergeCell ref="B3:C4"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="B7:C8"/>
@@ -1140,21 +1032,84 @@
     <mergeCell ref="D5:K6"/>
     <mergeCell ref="D7:K8"/>
     <mergeCell ref="D9:K10"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D15:K16"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="D11:K12"/>
+    <mergeCell ref="D13:K14"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="D3:K4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="74" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="40" max="11" man="1"/>
-  </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="12" max="92" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16510225-05EA-4CF9-9162-8201B6A31236}">
+  <dimension ref="A2:K5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:K2"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="68" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>